--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C8BAE75-26C9-4A21-A6C4-806A8A8F0318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEFB4C86-F998-4DF5-82EC-A2031937C481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
   <si>
     <t>Date</t>
   </si>
@@ -155,6 +155,33 @@
   </si>
   <si>
     <t>Stefan Kung</t>
+  </si>
+  <si>
+    <t>Matthew Brennan</t>
+  </si>
+  <si>
+    <t>Pau Miquel</t>
+  </si>
+  <si>
+    <t>Mads Pedersen</t>
+  </si>
+  <si>
+    <t>Hugo Hofstetter</t>
+  </si>
+  <si>
+    <t>Tobias Halland Johannessen</t>
+  </si>
+  <si>
+    <t>Axel Laurance</t>
+  </si>
+  <si>
+    <t>Oscar Onley</t>
+  </si>
+  <si>
+    <t>Orluis Aular</t>
+  </si>
+  <si>
+    <t>Ben Tulett</t>
   </si>
 </sst>
 </file>
@@ -668,6 +695,50 @@
         <v>44</v>
       </c>
     </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
     </row>

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEFB4C86-F998-4DF5-82EC-A2031937C481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72C3A99E-A2E2-4793-AC75-D0526728046A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="66">
   <si>
     <t>Date</t>
   </si>
@@ -182,6 +182,42 @@
   </si>
   <si>
     <t>Ben Tulett</t>
+  </si>
+  <si>
+    <t>Jarno Widar</t>
+  </si>
+  <si>
+    <t>Felix Gall</t>
+  </si>
+  <si>
+    <t>Sepp Kuss</t>
+  </si>
+  <si>
+    <t>Enric Mas</t>
+  </si>
+  <si>
+    <t>Primož Roglič</t>
+  </si>
+  <si>
+    <t>Richard Carapaz</t>
+  </si>
+  <si>
+    <t>Mattias Skjelmose</t>
+  </si>
+  <si>
+    <t>Gregor Mühlberger</t>
+  </si>
+  <si>
+    <t>Jay Vine</t>
+  </si>
+  <si>
+    <t>Ramses Debruyne</t>
+  </si>
+  <si>
+    <t>Lorenzo Fortunato</t>
+  </si>
+  <si>
+    <t>Koen Bouwman</t>
   </si>
 </sst>
 </file>
@@ -527,30 +563,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +701,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46256</v>
       </c>
@@ -695,7 +745,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46257</v>
       </c>
@@ -739,13 +789,122 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>46258</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5" t="s">
+        <v>62</v>
+      </c>
+      <c r="N5" t="s">
+        <v>63</v>
+      </c>
+      <c r="O5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>57</v>
+      </c>
+      <c r="R5" t="s">
+        <v>56</v>
+      </c>
+      <c r="S5" t="s">
+        <v>51</v>
+      </c>
+      <c r="T5" t="s">
+        <v>59</v>
+      </c>
+      <c r="U5" t="s">
+        <v>55</v>
+      </c>
+      <c r="V5" t="s">
+        <v>60</v>
+      </c>
+      <c r="W5" t="s">
+        <v>54</v>
+      </c>
+      <c r="X5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
     </row>
   </sheetData>

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72C3A99E-A2E2-4793-AC75-D0526728046A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{72C3A99E-A2E2-4793-AC75-D0526728046A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D027D34D-F452-4A87-B4E1-47FB50C79F31}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="72">
   <si>
     <t>Date</t>
   </si>
@@ -218,6 +218,24 @@
   </si>
   <si>
     <t>Koen Bouwman</t>
+  </si>
+  <si>
+    <t>Jordi Meeus</t>
+  </si>
+  <si>
+    <t>Vincenzo Albanese</t>
+  </si>
+  <si>
+    <t>Alberto Dainese</t>
+  </si>
+  <si>
+    <t>Vito Braet</t>
+  </si>
+  <si>
+    <t>David González</t>
+  </si>
+  <si>
+    <t>Bastien Tronchon</t>
   </si>
 </sst>
 </file>
@@ -563,44 +581,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="17" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="15" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -701,7 +719,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>46256</v>
       </c>
@@ -745,7 +763,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>46257</v>
       </c>
@@ -789,7 +807,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>46258</v>
       </c>
@@ -797,7 +815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>46259</v>
       </c>
@@ -898,13 +916,114 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" t="s">
+        <v>71</v>
+      </c>
+      <c r="O6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P6" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>57</v>
+      </c>
+      <c r="R6" t="s">
+        <v>56</v>
+      </c>
+      <c r="S6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T6" t="s">
+        <v>59</v>
+      </c>
+      <c r="U6" t="s">
+        <v>55</v>
+      </c>
+      <c r="V6" t="s">
+        <v>60</v>
+      </c>
+      <c r="W6" t="s">
+        <v>54</v>
+      </c>
+      <c r="X6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
     </row>
   </sheetData>

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{72C3A99E-A2E2-4793-AC75-D0526728046A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D027D34D-F452-4A87-B4E1-47FB50C79F31}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{72C3A99E-A2E2-4793-AC75-D0526728046A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C054B04-89DE-4B9E-A07C-0171BFF84DBA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="75">
   <si>
     <t>Date</t>
   </si>
@@ -236,6 +236,15 @@
   </si>
   <si>
     <t>Bastien Tronchon</t>
+  </si>
+  <si>
+    <t>Harold Tejada</t>
+  </si>
+  <si>
+    <t>Cristián Rodríguez</t>
+  </si>
+  <si>
+    <t>Clément Berthet</t>
   </si>
 </sst>
 </file>
@@ -583,39 +592,34 @@
   <dimension ref="A1:AG13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.3">
@@ -1015,6 +1019,107 @@
       </c>
       <c r="AG6" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" t="s">
+        <v>73</v>
+      </c>
+      <c r="K7" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" t="s">
+        <v>60</v>
+      </c>
+      <c r="M7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" t="s">
+        <v>51</v>
+      </c>
+      <c r="O7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P7" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>58</v>
+      </c>
+      <c r="R7" t="s">
+        <v>59</v>
+      </c>
+      <c r="S7" t="s">
+        <v>55</v>
+      </c>
+      <c r="T7" t="s">
+        <v>56</v>
+      </c>
+      <c r="U7" t="s">
+        <v>51</v>
+      </c>
+      <c r="V7" t="s">
+        <v>63</v>
+      </c>
+      <c r="W7" t="s">
+        <v>60</v>
+      </c>
+      <c r="X7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{72C3A99E-A2E2-4793-AC75-D0526728046A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C054B04-89DE-4B9E-A07C-0171BFF84DBA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC0908D-992D-4432-8DA8-1F01B141015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="85">
   <si>
     <t>Date</t>
   </si>
@@ -245,6 +245,36 @@
   </si>
   <si>
     <t>Clément Berthet</t>
+  </si>
+  <si>
+    <t>Andreas Leknessund</t>
+  </si>
+  <si>
+    <t>Jakob Omrzel</t>
+  </si>
+  <si>
+    <t>Juan Felipe Rodriguez</t>
+  </si>
+  <si>
+    <t>Iván Ramiro Sosa</t>
+  </si>
+  <si>
+    <t>Alexey Lutsenko</t>
+  </si>
+  <si>
+    <t>Eddie Dunbar</t>
+  </si>
+  <si>
+    <t>Raúl García Pierna</t>
+  </si>
+  <si>
+    <t>Valentin Paret-Peintre</t>
+  </si>
+  <si>
+    <t>Filippo Zana</t>
+  </si>
+  <si>
+    <t>Leo Bisiaux</t>
   </si>
 </sst>
 </file>
@@ -1122,6 +1152,107 @@
         <v>54</v>
       </c>
     </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M8" t="s">
+        <v>82</v>
+      </c>
+      <c r="N8" t="s">
+        <v>83</v>
+      </c>
+      <c r="O8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P8" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>58</v>
+      </c>
+      <c r="R8" t="s">
+        <v>55</v>
+      </c>
+      <c r="S8" t="s">
+        <v>56</v>
+      </c>
+      <c r="T8" t="s">
+        <v>51</v>
+      </c>
+      <c r="U8" t="s">
+        <v>59</v>
+      </c>
+      <c r="V8" t="s">
+        <v>60</v>
+      </c>
+      <c r="W8" t="s">
+        <v>72</v>
+      </c>
+      <c r="X8" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>84</v>
+      </c>
+    </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
     </row>

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC0908D-992D-4432-8DA8-1F01B141015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{1EC0908D-992D-4432-8DA8-1F01B141015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5712F60A-59C9-433D-83AE-184007BDCA24}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="90">
   <si>
     <t>Date</t>
   </si>
@@ -275,6 +275,21 @@
   </si>
   <si>
     <t>Leo Bisiaux</t>
+  </si>
+  <si>
+    <t>Bryan Coquard</t>
+  </si>
+  <si>
+    <t>Ben Turner</t>
+  </si>
+  <si>
+    <t>Jordan Labrosse</t>
+  </si>
+  <si>
+    <t>Matevž Govekar</t>
+  </si>
+  <si>
+    <t>Wout van Aert</t>
   </si>
 </sst>
 </file>
@@ -624,32 +639,32 @@
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="26" max="27" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.3">
@@ -1250,6 +1265,107 @@
         <v>76</v>
       </c>
       <c r="AG8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" t="s">
+        <v>69</v>
+      </c>
+      <c r="N9" t="s">
+        <v>88</v>
+      </c>
+      <c r="O9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P9" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>55</v>
+      </c>
+      <c r="R9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S9" t="s">
+        <v>51</v>
+      </c>
+      <c r="T9" t="s">
+        <v>59</v>
+      </c>
+      <c r="U9" t="s">
+        <v>60</v>
+      </c>
+      <c r="V9" t="s">
+        <v>72</v>
+      </c>
+      <c r="W9" t="s">
+        <v>61</v>
+      </c>
+      <c r="X9" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG9" t="s">
         <v>84</v>
       </c>
     </row>

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{1EC0908D-992D-4432-8DA8-1F01B141015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5712F60A-59C9-433D-83AE-184007BDCA24}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{1EC0908D-992D-4432-8DA8-1F01B141015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FCB8F84-9E83-4B0B-AC42-9D1C34E712B5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="91">
   <si>
     <t>Date</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>Wout van Aert</t>
+  </si>
+  <si>
+    <t>Santiago Buitrago</t>
   </si>
 </sst>
 </file>
@@ -1369,6 +1372,107 @@
         <v>84</v>
       </c>
     </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46264</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" t="s">
+        <v>90</v>
+      </c>
+      <c r="M10" t="s">
+        <v>56</v>
+      </c>
+      <c r="N10" t="s">
+        <v>61</v>
+      </c>
+      <c r="O10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>55</v>
+      </c>
+      <c r="R10" t="s">
+        <v>51</v>
+      </c>
+      <c r="S10" t="s">
+        <v>59</v>
+      </c>
+      <c r="T10" t="s">
+        <v>60</v>
+      </c>
+      <c r="U10" t="s">
+        <v>56</v>
+      </c>
+      <c r="V10" t="s">
+        <v>72</v>
+      </c>
+      <c r="W10" t="s">
+        <v>61</v>
+      </c>
+      <c r="X10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>54</v>
+      </c>
+    </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
     </row>

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{1EC0908D-992D-4432-8DA8-1F01B141015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FCB8F84-9E83-4B0B-AC42-9D1C34E712B5}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{1EC0908D-992D-4432-8DA8-1F01B141015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{464063CC-B056-47E5-BB98-050764288E39}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="95">
   <si>
     <t>Date</t>
   </si>
@@ -293,6 +293,18 @@
   </si>
   <si>
     <t>Santiago Buitrago</t>
+  </si>
+  <si>
+    <t>Magnus Cort</t>
+  </si>
+  <si>
+    <t>Thibau Nys</t>
+  </si>
+  <si>
+    <t>Xabier Mikel Azparren</t>
+  </si>
+  <si>
+    <t>Yevgeniy Fedorov</t>
   </si>
 </sst>
 </file>
@@ -638,39 +650,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="15" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -771,7 +779,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46256</v>
       </c>
@@ -815,7 +823,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46257</v>
       </c>
@@ -859,7 +867,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46258</v>
       </c>
@@ -867,7 +875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46259</v>
       </c>
@@ -968,7 +976,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46260</v>
       </c>
@@ -1069,7 +1077,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46261</v>
       </c>
@@ -1170,7 +1178,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46262</v>
       </c>
@@ -1271,7 +1279,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46263</v>
       </c>
@@ -1372,7 +1380,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46264</v>
       </c>
@@ -1473,13 +1481,111 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11" t="s">
+        <v>67</v>
+      </c>
+      <c r="N11" t="s">
+        <v>94</v>
+      </c>
+      <c r="O11" t="s">
+        <v>57</v>
+      </c>
+      <c r="P11" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>55</v>
+      </c>
+      <c r="R11" t="s">
+        <v>51</v>
+      </c>
+      <c r="S11" t="s">
+        <v>59</v>
+      </c>
+      <c r="T11" t="s">
+        <v>60</v>
+      </c>
+      <c r="U11" t="s">
+        <v>56</v>
+      </c>
+      <c r="V11" t="s">
+        <v>72</v>
+      </c>
+      <c r="W11" t="s">
+        <v>61</v>
+      </c>
+      <c r="X11" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
     </row>
   </sheetData>

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{1EC0908D-992D-4432-8DA8-1F01B141015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{464063CC-B056-47E5-BB98-050764288E39}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{1EC0908D-992D-4432-8DA8-1F01B141015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{465D16D9-1F0E-4628-8AD6-25ED172F0AD8}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>Yevgeniy Fedorov</t>
+  </si>
+  <si>
+    <t>Marc Brustenga</t>
   </si>
 </sst>
 </file>
@@ -1583,7 +1586,105 @@
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
+      <c r="A12" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" t="s">
+        <v>43</v>
+      </c>
+      <c r="K12" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" t="s">
+        <v>69</v>
+      </c>
+      <c r="N12" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" t="s">
+        <v>57</v>
+      </c>
+      <c r="P12" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>55</v>
+      </c>
+      <c r="R12" t="s">
+        <v>51</v>
+      </c>
+      <c r="S12" t="s">
+        <v>59</v>
+      </c>
+      <c r="T12" t="s">
+        <v>60</v>
+      </c>
+      <c r="U12" t="s">
+        <v>56</v>
+      </c>
+      <c r="V12" t="s">
+        <v>72</v>
+      </c>
+      <c r="W12" t="s">
+        <v>61</v>
+      </c>
+      <c r="X12" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{1EC0908D-992D-4432-8DA8-1F01B141015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{465D16D9-1F0E-4628-8AD6-25ED172F0AD8}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{1EC0908D-992D-4432-8DA8-1F01B141015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{353659DD-94A7-4D36-9974-179B7457D7C1}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="99">
   <si>
     <t>Date</t>
   </si>
@@ -308,15 +308,21 @@
   </si>
   <si>
     <t>Marc Brustenga</t>
+  </si>
+  <si>
+    <t>Urko Berrade</t>
+  </si>
+  <si>
+    <t>Mauri Vansevenant</t>
+  </si>
+  <si>
+    <t>José Manuel Díaz</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
-  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -346,9 +352,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -783,7 +788,7 @@
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>46256</v>
       </c>
       <c r="B2">
@@ -827,7 +832,7 @@
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>46257</v>
       </c>
       <c r="B3">
@@ -871,7 +876,7 @@
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>46258</v>
       </c>
       <c r="B4">
@@ -879,7 +884,7 @@
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>46259</v>
       </c>
       <c r="B5">
@@ -980,7 +985,7 @@
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>46260</v>
       </c>
       <c r="B6">
@@ -1081,7 +1086,7 @@
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>46261</v>
       </c>
       <c r="B7">
@@ -1182,7 +1187,7 @@
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>46262</v>
       </c>
       <c r="B8">
@@ -1283,7 +1288,7 @@
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>46263</v>
       </c>
       <c r="B9">
@@ -1384,7 +1389,7 @@
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>46264</v>
       </c>
       <c r="B10">
@@ -1485,7 +1490,7 @@
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>46266</v>
       </c>
       <c r="B11">
@@ -1586,7 +1591,7 @@
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>46267</v>
       </c>
       <c r="B12">
@@ -1687,10 +1692,109 @@
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+      <c r="A13" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H13" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" t="s">
+        <v>98</v>
+      </c>
+      <c r="N13" t="s">
+        <v>51</v>
+      </c>
+      <c r="O13" t="s">
+        <v>57</v>
+      </c>
+      <c r="P13" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>55</v>
+      </c>
+      <c r="R13" t="s">
+        <v>59</v>
+      </c>
+      <c r="S13" t="s">
+        <v>51</v>
+      </c>
+      <c r="T13" t="s">
+        <v>76</v>
+      </c>
+      <c r="U13" t="s">
+        <v>60</v>
+      </c>
+      <c r="V13" t="s">
+        <v>56</v>
+      </c>
+      <c r="W13" t="s">
+        <v>61</v>
+      </c>
+      <c r="X13" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>84</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{1EC0908D-992D-4432-8DA8-1F01B141015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{353659DD-94A7-4D36-9974-179B7457D7C1}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{1EC0908D-992D-4432-8DA8-1F01B141015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCD37E4E-4AC3-410C-A4FD-5B3A440334AD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -317,6 +317,18 @@
   </si>
   <si>
     <t>José Manuel Díaz</t>
+  </si>
+  <si>
+    <t>Kevin Vermaerke</t>
+  </si>
+  <si>
+    <t>Simon Dalby</t>
+  </si>
+  <si>
+    <t>Jesús Herrada</t>
+  </si>
+  <si>
+    <t>Andreas Kron</t>
   </si>
 </sst>
 </file>
@@ -657,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG13"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1792,6 +1804,107 @@
         <v>84</v>
       </c>
     </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" t="s">
+        <v>99</v>
+      </c>
+      <c r="J14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K14" t="s">
+        <v>100</v>
+      </c>
+      <c r="L14" t="s">
+        <v>83</v>
+      </c>
+      <c r="M14" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" t="s">
+        <v>102</v>
+      </c>
+      <c r="O14" t="s">
+        <v>57</v>
+      </c>
+      <c r="P14" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>55</v>
+      </c>
+      <c r="R14" t="s">
+        <v>59</v>
+      </c>
+      <c r="S14" t="s">
+        <v>51</v>
+      </c>
+      <c r="T14" t="s">
+        <v>76</v>
+      </c>
+      <c r="U14" t="s">
+        <v>60</v>
+      </c>
+      <c r="V14" t="s">
+        <v>56</v>
+      </c>
+      <c r="W14" t="s">
+        <v>72</v>
+      </c>
+      <c r="X14" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t>Date</t>
   </si>
@@ -329,6 +329,36 @@
   </si>
   <si>
     <t>Andreas Kron</t>
+  </si>
+  <si>
+    <t>Marco Brenner</t>
+  </si>
+  <si>
+    <t>Jørgen Nordhagen</t>
+  </si>
+  <si>
+    <t>Walter Calzoni</t>
+  </si>
+  <si>
+    <t>João Almeida</t>
+  </si>
+  <si>
+    <t>Guillaume Martin</t>
+  </si>
+  <si>
+    <t>Alessandro Covi</t>
+  </si>
+  <si>
+    <t>Henok Mulubrhan</t>
+  </si>
+  <si>
+    <t>Stefan Küng</t>
+  </si>
+  <si>
+    <t>Ivo Oliveira</t>
+  </si>
+  <si>
+    <t>Mats Wenzel</t>
   </si>
 </sst>
 </file>
@@ -669,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG14"/>
+  <dimension ref="A1:AG16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1905,6 +1935,208 @@
         <v>84</v>
       </c>
     </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>46270</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" t="s">
+        <v>74</v>
+      </c>
+      <c r="I15" t="s">
+        <v>104</v>
+      </c>
+      <c r="J15" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" t="s">
+        <v>105</v>
+      </c>
+      <c r="L15" t="s">
+        <v>106</v>
+      </c>
+      <c r="M15" t="s">
+        <v>107</v>
+      </c>
+      <c r="N15" t="s">
+        <v>65</v>
+      </c>
+      <c r="O15" t="s">
+        <v>57</v>
+      </c>
+      <c r="P15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>58</v>
+      </c>
+      <c r="R15" t="s">
+        <v>59</v>
+      </c>
+      <c r="S15" t="s">
+        <v>51</v>
+      </c>
+      <c r="T15" t="s">
+        <v>76</v>
+      </c>
+      <c r="U15" t="s">
+        <v>60</v>
+      </c>
+      <c r="V15" t="s">
+        <v>73</v>
+      </c>
+      <c r="W15" t="s">
+        <v>74</v>
+      </c>
+      <c r="X15" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46271</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" t="s">
+        <v>108</v>
+      </c>
+      <c r="I16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" t="s">
+        <v>109</v>
+      </c>
+      <c r="K16" t="s">
+        <v>110</v>
+      </c>
+      <c r="L16" t="s">
+        <v>111</v>
+      </c>
+      <c r="M16" t="s">
+        <v>41</v>
+      </c>
+      <c r="N16" t="s">
+        <v>112</v>
+      </c>
+      <c r="O16" t="s">
+        <v>57</v>
+      </c>
+      <c r="P16" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>58</v>
+      </c>
+      <c r="R16" t="s">
+        <v>59</v>
+      </c>
+      <c r="S16" t="s">
+        <v>51</v>
+      </c>
+      <c r="T16" t="s">
+        <v>76</v>
+      </c>
+      <c r="U16" t="s">
+        <v>60</v>
+      </c>
+      <c r="V16" t="s">
+        <v>73</v>
+      </c>
+      <c r="W16" t="s">
+        <v>74</v>
+      </c>
+      <c r="X16" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{1EC0908D-992D-4432-8DA8-1F01B141015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCD37E4E-4AC3-410C-A4FD-5B3A440334AD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D97D4D6-3DB4-46D0-B8E0-76329EE67857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="115">
   <si>
     <t>Date</t>
   </si>
@@ -359,6 +359,12 @@
   </si>
   <si>
     <t>Mats Wenzel</t>
+  </si>
+  <si>
+    <t>César Macías</t>
+  </si>
+  <si>
+    <t>Marcel Camprubí</t>
   </si>
 </sst>
 </file>
@@ -699,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG16"/>
+  <dimension ref="A1:AG17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -2137,6 +2143,107 @@
         <v>84</v>
       </c>
     </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" t="s">
+        <v>67</v>
+      </c>
+      <c r="K17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L17" t="s">
+        <v>113</v>
+      </c>
+      <c r="M17" t="s">
+        <v>114</v>
+      </c>
+      <c r="N17" t="s">
+        <v>95</v>
+      </c>
+      <c r="O17" t="s">
+        <v>57</v>
+      </c>
+      <c r="P17" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>58</v>
+      </c>
+      <c r="R17" t="s">
+        <v>59</v>
+      </c>
+      <c r="S17" t="s">
+        <v>51</v>
+      </c>
+      <c r="T17" t="s">
+        <v>76</v>
+      </c>
+      <c r="U17" t="s">
+        <v>60</v>
+      </c>
+      <c r="V17" t="s">
+        <v>73</v>
+      </c>
+      <c r="W17" t="s">
+        <v>74</v>
+      </c>
+      <c r="X17" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D97D4D6-3DB4-46D0-B8E0-76329EE67857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{4D97D4D6-3DB4-46D0-B8E0-76329EE67857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E178912E-D5D3-424F-9583-BAA86933BBDA}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="116">
   <si>
     <t>Date</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>Marcel Camprubí</t>
+  </si>
+  <si>
+    <t>Steffen De Schuyteneer</t>
   </si>
 </sst>
 </file>
@@ -705,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG17"/>
+  <dimension ref="A1:AG18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -2244,6 +2247,107 @@
         <v>84</v>
       </c>
     </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" t="s">
+        <v>50</v>
+      </c>
+      <c r="I18" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18" t="s">
+        <v>113</v>
+      </c>
+      <c r="K18" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" t="s">
+        <v>85</v>
+      </c>
+      <c r="M18" t="s">
+        <v>68</v>
+      </c>
+      <c r="N18" t="s">
+        <v>108</v>
+      </c>
+      <c r="O18" t="s">
+        <v>57</v>
+      </c>
+      <c r="P18" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>58</v>
+      </c>
+      <c r="R18" t="s">
+        <v>59</v>
+      </c>
+      <c r="S18" t="s">
+        <v>51</v>
+      </c>
+      <c r="T18" t="s">
+        <v>76</v>
+      </c>
+      <c r="U18" t="s">
+        <v>60</v>
+      </c>
+      <c r="V18" t="s">
+        <v>73</v>
+      </c>
+      <c r="W18" t="s">
+        <v>74</v>
+      </c>
+      <c r="X18" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{4D97D4D6-3DB4-46D0-B8E0-76329EE67857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E178912E-D5D3-424F-9583-BAA86933BBDA}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{4D97D4D6-3DB4-46D0-B8E0-76329EE67857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{855FD35A-9E99-4B42-9684-37127F9029CF}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="118">
   <si>
     <t>Date</t>
   </si>
@@ -368,6 +368,12 @@
   </si>
   <si>
     <t>Steffen De Schuyteneer</t>
+  </si>
+  <si>
+    <t>Bruno Armirail</t>
+  </si>
+  <si>
+    <t>Georg Steinhauser</t>
   </si>
 </sst>
 </file>
@@ -708,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG18"/>
+  <dimension ref="A1:AG19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -2348,6 +2354,107 @@
         <v>84</v>
       </c>
     </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" t="s">
+        <v>41</v>
+      </c>
+      <c r="I19" t="s">
+        <v>116</v>
+      </c>
+      <c r="J19" t="s">
+        <v>111</v>
+      </c>
+      <c r="K19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L19" t="s">
+        <v>93</v>
+      </c>
+      <c r="M19" t="s">
+        <v>117</v>
+      </c>
+      <c r="N19" t="s">
+        <v>57</v>
+      </c>
+      <c r="O19" t="s">
+        <v>57</v>
+      </c>
+      <c r="P19" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>55</v>
+      </c>
+      <c r="R19" t="s">
+        <v>59</v>
+      </c>
+      <c r="S19" t="s">
+        <v>51</v>
+      </c>
+      <c r="T19" t="s">
+        <v>76</v>
+      </c>
+      <c r="U19" t="s">
+        <v>74</v>
+      </c>
+      <c r="V19" t="s">
+        <v>60</v>
+      </c>
+      <c r="W19" t="s">
+        <v>73</v>
+      </c>
+      <c r="X19" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{4D97D4D6-3DB4-46D0-B8E0-76329EE67857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{855FD35A-9E99-4B42-9684-37127F9029CF}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{4D97D4D6-3DB4-46D0-B8E0-76329EE67857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC31BFAC-89E4-48B4-AFB0-6979E7DDD173}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="122">
   <si>
     <t>Date</t>
   </si>
@@ -374,6 +374,18 @@
   </si>
   <si>
     <t>Georg Steinhauser</t>
+  </si>
+  <si>
+    <t>Thomas Gloag</t>
+  </si>
+  <si>
+    <t>Chris Hamilton</t>
+  </si>
+  <si>
+    <t>Sergio Samitier</t>
+  </si>
+  <si>
+    <t>Rudy Molard</t>
   </si>
 </sst>
 </file>
@@ -714,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG19"/>
+  <dimension ref="A1:AG20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -2455,6 +2467,107 @@
         <v>84</v>
       </c>
     </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" t="s">
+        <v>107</v>
+      </c>
+      <c r="J20" t="s">
+        <v>119</v>
+      </c>
+      <c r="K20" t="s">
+        <v>99</v>
+      </c>
+      <c r="L20" t="s">
+        <v>120</v>
+      </c>
+      <c r="M20" t="s">
+        <v>121</v>
+      </c>
+      <c r="N20" t="s">
+        <v>55</v>
+      </c>
+      <c r="O20" t="s">
+        <v>57</v>
+      </c>
+      <c r="P20" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>55</v>
+      </c>
+      <c r="R20" t="s">
+        <v>59</v>
+      </c>
+      <c r="S20" t="s">
+        <v>51</v>
+      </c>
+      <c r="T20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U20" t="s">
+        <v>74</v>
+      </c>
+      <c r="V20" t="s">
+        <v>73</v>
+      </c>
+      <c r="W20" t="s">
+        <v>60</v>
+      </c>
+      <c r="X20" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
